--- a/Models/CLIP/male1data/clip_big5_male1_long_hair.xlsx
+++ b/Models/CLIP/male1data/clip_big5_male1_long_hair.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucs-my.sharepoint.com/personal/yq_c_tamu_edu/Documents/Research/genderBias/GenderBias-SRL-Implementation/Models/CLIP/male1data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_302582AD51BE5BC0C846FC90A3509072624A525E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{158FEF20-9266-4180-B794-B286A2EE72A3}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Extraversion" sheetId="1" r:id="rId1"/>
@@ -13,12 +19,25 @@
     <sheet name="Neuroticism" sheetId="4" r:id="rId4"/>
     <sheet name="Openness" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="48">
   <si>
     <t>Positive Trait</t>
   </si>
@@ -159,14 +178,25 @@
   </si>
   <si>
     <t>Likes to reflect, play with ideas</t>
+  </si>
+  <si>
+    <t>avg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -194,21 +224,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -246,7 +285,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -280,6 +319,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -314,9 +354,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -489,11 +530,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,62 +548,75 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.07230253517627716</v>
+        <v>7.2302535176277161E-2</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
       </c>
       <c r="D2">
-        <v>0.005659619346261024</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>5.6596193462610236E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.02651165053248405</v>
+        <v>2.6511650532484051E-2</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>0.001300068572163582</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>1.3000685721635821E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.01138296164572239</v>
+        <v>1.1382961645722389E-2</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>0.0009266854031011462</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>9.2668540310114622E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.01015690341591835</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>1.015690341591835E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6">
-        <v>0.003863251768052578</v>
+        <v>3.863251768052578E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1">
+        <f>AVERAGE(B2:B6)</f>
+        <v>2.4843460507690908E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <f>AVERAGE(D2:D6)</f>
+        <v>2.628791107175251E-3</v>
       </c>
     </row>
   </sheetData>
@@ -571,11 +625,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.90625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -589,68 +647,81 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2">
-        <v>0.07110803574323654</v>
+        <v>7.1108035743236542E-2</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
       <c r="D2">
-        <v>0.007137542124837637</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>7.1375421248376369E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3">
-        <v>0.01094112545251846</v>
+        <v>1.094112545251846E-2</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
       <c r="D3">
-        <v>0.006543945521116257</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>6.5439455211162567E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4">
-        <v>0.00953743327409029</v>
+        <v>9.5374332740902901E-3</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4">
-        <v>0.003793547861278057</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>3.7935478612780571E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5">
-        <v>0.008148515596985817</v>
+        <v>8.148515596985817E-3</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5">
-        <v>0.001124645699746907</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>1.124645699746907E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
       <c r="B6">
-        <v>0.004182201810181141</v>
+        <v>4.1822018101811409E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1">
+        <f>AVERAGE(B2:B6)</f>
+        <v>2.0783462375402451E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <f>AVERAGE(D2:D6)</f>
+        <v>4.6499203017447144E-3</v>
       </c>
     </row>
   </sheetData>
@@ -659,11 +730,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="37.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -677,68 +752,81 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2">
-        <v>0.07343581318855286</v>
+        <v>7.3435813188552856E-2</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2">
-        <v>0.002096315147355199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>2.0963151473551989E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
       <c r="B3">
-        <v>0.0117822578176856</v>
+        <v>1.1782257817685601E-2</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
       </c>
       <c r="D3">
-        <v>0.00162620039191097</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>1.62620039191097E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
       <c r="B4">
-        <v>0.005660525988787413</v>
+        <v>5.6605259887874126E-3</v>
       </c>
       <c r="C4" t="s">
         <v>28</v>
       </c>
       <c r="D4">
-        <v>0.001096432912163436</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>1.096432912163436E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
       <c r="B5">
-        <v>0.002183251548558474</v>
+        <v>2.183251548558474E-3</v>
       </c>
       <c r="C5" t="s">
         <v>29</v>
       </c>
       <c r="D5">
-        <v>0.0002273603313369676</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>2.2736033133696759E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6">
-        <v>0.000599467835854739</v>
+        <v>5.9946783585473895E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1">
+        <f>AVERAGE(B2:B6)</f>
+        <v>1.8732263275887819E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <f>AVERAGE(D2:D6)</f>
+        <v>1.2615771956916433E-3</v>
       </c>
     </row>
   </sheetData>
@@ -747,11 +835,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="32.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -765,62 +857,75 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>30</v>
       </c>
       <c r="B2">
-        <v>0.06802345812320709</v>
+        <v>6.8023458123207092E-2</v>
       </c>
       <c r="C2" t="s">
         <v>33</v>
       </c>
       <c r="D2">
-        <v>0.007346070371568203</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>7.346070371568203E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>31</v>
       </c>
       <c r="B3">
-        <v>0.05444684624671936</v>
+        <v>5.444684624671936E-2</v>
       </c>
       <c r="C3" t="s">
         <v>34</v>
       </c>
       <c r="D3">
-        <v>0.004128529224544764</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>4.1285292245447644E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>32</v>
       </c>
       <c r="B4">
-        <v>0.02063198015093803</v>
+        <v>2.0631980150938031E-2</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
       </c>
       <c r="D4">
-        <v>0.003849453059956431</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>3.849453059956431E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>36</v>
       </c>
       <c r="D5">
-        <v>0.003536454401910305</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>3.536454401910305E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>37</v>
       </c>
       <c r="D6">
-        <v>0.001816806849092245</v>
+        <v>1.8168068490922451E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1">
+        <f>AVERAGE(B2:B6)</f>
+        <v>4.7700761506954827E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <f>AVERAGE(D2:D6)</f>
+        <v>4.1354627814143893E-3</v>
       </c>
     </row>
   </sheetData>
@@ -829,11 +934,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="35.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -847,7 +956,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -861,58 +970,71 @@
         <v>0.2314382791519165</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>39</v>
       </c>
       <c r="B3">
-        <v>0.08314815163612366</v>
+        <v>8.3148151636123657E-2</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
       </c>
       <c r="D3">
-        <v>0.01505789998918772</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>1.5057899989187719E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>40</v>
       </c>
       <c r="B4">
-        <v>0.01472592819482088</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>1.4725928194820879E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>41</v>
       </c>
       <c r="B5">
-        <v>0.009243362583220005</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>9.243362583220005E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>42</v>
       </c>
       <c r="B6">
-        <v>0.008191993460059166</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>8.191993460059166E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>43</v>
       </c>
       <c r="B7">
-        <v>0.001499369624070823</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>1.499369624070823E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>44</v>
       </c>
       <c r="B8">
-        <v>0.0009014987153932452</v>
+        <v>9.0149871539324522E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1">
+        <f>AVERAGE(B2:B8)</f>
+        <v>3.377084390792464E-2</v>
+      </c>
+      <c r="D9" s="1">
+        <f>AVERAGE(D2:D8)</f>
+        <v>0.12324808957055211</v>
       </c>
     </row>
   </sheetData>
